--- a/src/jira_cards.xlsx
+++ b/src/jira_cards.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,7 +659,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A Produzir</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MANTA-30807</t>
+          <t>MANTA-30813</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30807</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30813</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30439 PEDIDO AVULSO</t>
+          <t>REBLINDAGEM - 1042448 - SUPPLY 114133</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -749,11 +749,6 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>🟢RECEBIDO LIBERADO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
         </is>
       </c>
     </row>
@@ -780,7 +775,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A Produzir</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3322,7 +3317,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MANTA-30526</t>
+          <t>MANTA-30521</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3332,12 +3327,12 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30526</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30521</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3352,19 +3347,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MANTA-30525</t>
+          <t>MANTA-30515</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3374,12 +3369,12 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30525</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30515</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30934</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3394,19 +3389,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MANTA-30523</t>
+          <t>MANTA-30514</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3416,12 +3411,12 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30523</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30514</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>30923</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3436,19 +3431,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MANTA-30521</t>
+          <t>MANTA-30513</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3458,12 +3453,12 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30521</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30513</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3478,7 +3473,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3490,7 +3485,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MANTA-30515</t>
+          <t>MANTA-30512</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3500,12 +3495,12 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30515</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3520,7 +3515,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3532,7 +3527,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MANTA-30514</t>
+          <t>MANTA-30511</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3542,12 +3537,12 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30514</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>30923</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3562,7 +3557,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3574,7 +3569,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MANTA-30513</t>
+          <t>MANTA-30510</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3584,12 +3579,12 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30513</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30510</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3604,7 +3599,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3616,7 +3611,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MANTA-30512</t>
+          <t>MANTA-30509</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3626,12 +3621,12 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3641,12 +3636,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3658,7 +3653,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MANTA-30511</t>
+          <t>MANTA-30507</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3668,12 +3663,12 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30507</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>30920</t>
+          <t>30916</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3688,7 +3683,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3700,7 +3695,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MANTA-30510</t>
+          <t>MANTA-30506</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3710,12 +3705,12 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30510</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30506</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30919</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3735,14 +3730,14 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MANTA-30509</t>
+          <t>MANTA-30505</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3752,12 +3747,12 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>30918</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3767,7 +3762,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3784,7 +3779,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MANTA-30507</t>
+          <t>MANTA-30504</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3794,12 +3789,12 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30507</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30504</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30916</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3809,24 +3804,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>JAECOO - JAECOO 7 SUV - 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MANTA-30506</t>
+          <t>MANTA-30479</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3836,12 +3831,12 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30506</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30479</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>30915</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3851,12 +3846,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>LEXUS - NX 350 H SUV - 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3868,7 +3863,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MANTA-30505</t>
+          <t>MANTA-30469</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3878,12 +3873,12 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30469</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3893,24 +3888,24 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>MINI - COOPER 04 PORTAS HATCH - 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MANTA-30504</t>
+          <t>MANTA-30464</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3920,12 +3915,12 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30504</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30464</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3935,12 +3930,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JAECOO - JAECOO 7 SUV - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3952,7 +3947,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MANTA-30479</t>
+          <t>MANTA-30463</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3962,12 +3957,12 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30479</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30892</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3977,24 +3972,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LEXUS - NX 350 H SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MANTA-30469</t>
+          <t>MANTA-30462</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4004,12 +3999,12 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30469</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30462</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30882</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4019,12 +4014,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MINI - COOPER 04 PORTAS HATCH - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4036,7 +4031,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MANTA-30464</t>
+          <t>MANTA-30452</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4046,12 +4041,12 @@
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30464</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30877</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4061,7 +4056,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4071,14 +4066,14 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MANTA-30463</t>
+          <t>MANTA-30451</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4088,12 +4083,12 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30451</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4103,24 +4098,24 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>KIA - CARNIVAL VAN - 2025</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MANTA-30462</t>
+          <t>MANTA-30428</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4130,12 +4125,12 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30462</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4150,19 +4145,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MANTA-30452</t>
+          <t>MANTA-30421</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4172,12 +4167,12 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>30834</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4187,12 +4182,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4204,7 +4199,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MANTA-30451</t>
+          <t>MANTA-30420</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4214,12 +4209,12 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30451</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4229,24 +4224,24 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>KIA - CARNIVAL VAN - 2025</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MANTA-30428</t>
+          <t>MANTA-30367</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4256,12 +4251,12 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4288,7 +4283,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MANTA-30421</t>
+          <t>MANTA-30257</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4298,12 +4293,12 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4313,12 +4308,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4330,7 +4325,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MANTA-30420</t>
+          <t>MANTA-30242</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4340,12 +4335,12 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4360,7 +4355,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4372,7 +4367,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MANTA-30367</t>
+          <t>MANTA-30224</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4382,12 +4377,12 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4397,12 +4392,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4414,7 +4409,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MANTA-30309</t>
+          <t>MANTA-30196</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4424,12 +4419,12 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30309</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>30735</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4444,7 +4439,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4456,7 +4451,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MANTA-30257</t>
+          <t>MANTA-30191</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4466,12 +4461,12 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30191</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>30628</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4486,19 +4481,19 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
+          <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MANTA-30242</t>
+          <t>MANTA-30026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4508,12 +4503,12 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4523,24 +4518,24 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MANTA-30224</t>
+          <t>MANTA-29945</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4550,12 +4545,12 @@
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29945</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4570,19 +4565,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
+          <t>GWM - HAVAL H6 HEV 2 - 2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MANTA-30196</t>
+          <t>MANTA-29923</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4592,12 +4587,12 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4617,14 +4612,14 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MANTA-30191</t>
+          <t>MANTA-29866</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4634,12 +4629,12 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30191</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4654,19 +4649,19 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BMW - X3 SUV - 2026</t>
+          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MANTA-30026</t>
+          <t>MANTA-29816</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4676,39 +4671,34 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30026</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>JEEP - COMMANDER SUV - 2026</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MANTA-29945</t>
+          <t>MANTA-29792</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4718,39 +4708,34 @@
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29945</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H6 HEV 2 - 2026</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MANTA-29923</t>
+          <t>MANTA-29372</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4760,12 +4745,12 @@
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4792,7 +4777,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MANTA-29866</t>
+          <t>MANTA-27100</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4802,12 +4787,12 @@
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-27100</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4822,136 +4807,10 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
+          <t>LEXUS - RX 500H SUV - 2025</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>MANTA-29791</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29791</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>30281</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>🟢RECEBIDO LIBERADO</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>MERCEDES-BENZ - GLS SUV - 2026</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>MANTA-29372</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>29901</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>🟢RECEBIDO LIBERADO</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>MANTA-27100</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Manta</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-27100</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>28192</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Liberado Engenharia</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>LEXUS - RX 500H SUV - 2025</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
         <is>
           <t>10/03/2026</t>
         </is>
@@ -5063,9 +4922,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/jira_cards.xlsx
+++ b/src/jira_cards.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aguardando Corte</t>
+          <t>Aguardando montagem</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TENSYLON-799</t>
+          <t>TENSYLON-801</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-799</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-801</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aguardando Autoclave</t>
+          <t>Aguardando montagem</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,19 +585,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PORSCHE - CAYENNE COUPE - 2026</t>
+          <t>KIA - CARNIVAL VAN - 2025</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TENSYLON-796</t>
+          <t>TENSYLON-799</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -607,27 +607,27 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-796</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-799</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30828</t>
+          <t>30840</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aguardando Acabamento</t>
+          <t>Aguardando Autoclave</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BMW - X6 SUV - 2026</t>
+          <t>PORSCHE - CAYENNE COUPE - 2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TENSYLON-794</t>
+          <t>TENSYLON-796</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-794</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-796</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PORSCHE - CAYENNE COUPE - 2025</t>
+          <t>BMW - X6 SUV - 2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TENSYLON-761</t>
+          <t>TENSYLON-794</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -691,39 +691,39 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-761</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-794</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aguardando montagem</t>
+          <t>Aguardando Acabamento</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BMW - X3 SUV - 2026</t>
+          <t>PORSCHE - CAYENNE COUPE - 2025</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TENSYLON-752</t>
+          <t>TENSYLON-761</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-752</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-761</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>30628</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aguardando Acabamento</t>
+          <t>Aguardando montagem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -753,19 +753,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AUDI - SQ6 E-TRON SPORTBACK - 2025</t>
+          <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TENSYLON-746</t>
+          <t>TENSYLON-752</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-746</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-752</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>30580</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PORSCHE - 911 - 2025</t>
+          <t>AUDI - SQ6 E-TRON SPORTBACK - 2025</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TENSYLON-730</t>
+          <t>TENSYLON-746</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -817,39 +817,39 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-730</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-746</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aguardando montagem</t>
+          <t>Aguardando Acabamento</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JEEP - COMMANDER SUV - 2026</t>
+          <t>PORSCHE - 911 - 2025</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TENSYLON-691</t>
+          <t>TENSYLON-730</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -859,39 +859,39 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-691</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-730</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aguardando Acabamento</t>
+          <t>Aguardando montagem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GWM - HAVAL H9 SUV - 2026</t>
+          <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TENSYLON-674</t>
+          <t>TENSYLON-691</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/TENSYLON-674</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-691</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30351</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ - GLS SUV - 2026</t>
+          <t>GWM - HAVAL H9 SUV - 2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -933,32 +933,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MANTA-30813</t>
+          <t>TENSYLON-674</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manta</t>
+          <t>Tensylon</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30813</t>
+          <t>https://carboncars.atlassian.net/browse/TENSYLON-674</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>REBLINDAGEM - 1042448 - SUPPLY 114133</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>Aguardando Acabamento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ - GLS SUV - 2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -970,7 +975,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MANTA-30781</t>
+          <t>MANTA-30763</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -980,12 +985,12 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30781</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30763</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30911 PED AVULSO</t>
+          <t>31136 - ALT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1000,19 +1005,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>VOLVO - XC90 - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MANTA-30763</t>
+          <t>MANTA-30759</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,12 +1027,12 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30763</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30759</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31136 - ALT</t>
+          <t>30993 - ALT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1042,12 +1047,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>BMW - X1 SUV - 2026</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MANTA-30720</t>
+          <t>MANTA-30722</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30720</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30722</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30931 - ALT</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1457,24 +1457,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>TOYOTA - SW4 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MANTA-30718</t>
+          <t>MANTA-30720</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1484,12 +1479,12 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30718</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30720</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31120</t>
+          <t>30931 - ALT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1499,7 +1494,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1516,7 +1511,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MANTA-30658</t>
+          <t>MANTA-30718</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1526,12 +1521,12 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30658</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30718</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>31120</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1541,7 +1536,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1558,7 +1553,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MANTA-30657</t>
+          <t>MANTA-30670</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1568,12 +1563,12 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30657</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30670</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1588,19 +1583,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>GWM - HAVAL H6 HEV 2 - 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MANTA-30656</t>
+          <t>MANTA-30667</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1610,12 +1600,12 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30656</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30667</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1630,19 +1620,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MANTA-30649</t>
+          <t>MANTA-30658</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1652,12 +1637,12 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30649</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30658</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>31054</t>
+          <t>31061</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1667,12 +1652,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1684,7 +1669,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MANTA-30624</t>
+          <t>MANTA-30657</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1694,12 +1679,12 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30624</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30657</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1709,12 +1694,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1726,7 +1711,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MANTA-30622</t>
+          <t>MANTA-30656</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1736,12 +1721,12 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30622</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30656</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1756,7 +1741,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1768,7 +1753,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MANTA-30619</t>
+          <t>MANTA-30650</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1778,12 +1763,12 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30619</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30650</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1798,19 +1783,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>FORD - TERRITORY - 2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MANTA-30615</t>
+          <t>MANTA-30649</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1820,12 +1800,12 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30615</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30649</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31021</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1840,7 +1820,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1852,7 +1832,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MANTA-30613</t>
+          <t>MANTA-30636</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1862,12 +1842,12 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30613</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30636</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>31041</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1877,24 +1857,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>FORD - MUSTANG GT - 2025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MANTA-30610</t>
+          <t>MANTA-30624</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1904,12 +1879,12 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30610</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30624</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1919,12 +1894,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1936,7 +1911,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MANTA-30609</t>
+          <t>MANTA-30622</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1946,12 +1921,12 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30609</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30622</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1966,7 +1941,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1978,7 +1953,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MANTA-30608</t>
+          <t>MANTA-30619</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1988,12 +1963,12 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30608</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30619</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2008,7 +1983,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2020,7 +1995,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MANTA-30607</t>
+          <t>MANTA-30615</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2030,12 +2005,12 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30607</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30615</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31013</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2050,7 +2025,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2062,7 +2037,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MANTA-30606</t>
+          <t>MANTA-30613</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2072,12 +2047,12 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30606</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30613</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>31019</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2104,7 +2079,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MANTA-30602</t>
+          <t>MANTA-30610</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2114,12 +2089,12 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30602</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30610</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>31016</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2146,7 +2121,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MANTA-30600</t>
+          <t>MANTA-30609</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2156,12 +2131,12 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30600</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30609</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2188,7 +2163,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MANTA-30595</t>
+          <t>MANTA-30608</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2198,12 +2173,12 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30595</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30608</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31001</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2218,7 +2193,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2230,7 +2205,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MANTA-30594</t>
+          <t>MANTA-30607</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2240,12 +2215,12 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30594</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30607</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2255,7 +2230,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2272,7 +2247,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MANTA-30593</t>
+          <t>MANTA-30606</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2282,12 +2257,12 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30593</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30606</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>30999</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2302,7 +2277,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2314,7 +2289,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MANTA-30590</t>
+          <t>MANTA-30602</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2324,12 +2299,12 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30590</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30602</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>31009</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2339,12 +2314,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2356,7 +2331,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MANTA-30586</t>
+          <t>MANTA-30600</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2366,12 +2341,12 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30586</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30600</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2398,7 +2373,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MANTA-30585</t>
+          <t>MANTA-30595</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2408,12 +2383,12 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30585</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30595</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2428,7 +2403,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2440,7 +2415,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MANTA-30584</t>
+          <t>MANTA-30594</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,12 +2425,12 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30584</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30594</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2482,7 +2457,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MANTA-30583</t>
+          <t>MANTA-30593</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2492,12 +2467,12 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30583</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30593</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2524,7 +2499,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MANTA-30582</t>
+          <t>MANTA-30590</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2534,12 +2509,12 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30582</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30590</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30988</t>
+          <t>30996</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2566,7 +2541,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MANTA-30581</t>
+          <t>MANTA-30586</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2576,12 +2551,12 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30581</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30586</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>30992</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2596,7 +2571,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2608,7 +2583,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MANTA-30580</t>
+          <t>MANTA-30585</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2618,12 +2593,12 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30580</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30585</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2638,7 +2613,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2650,7 +2625,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MANTA-30579</t>
+          <t>MANTA-30584</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2660,12 +2635,12 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30579</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30584</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>30985</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2692,7 +2667,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MANTA-30578</t>
+          <t>MANTA-30583</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2702,12 +2677,12 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30578</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30583</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2734,7 +2709,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MANTA-30577</t>
+          <t>MANTA-30582</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2744,12 +2719,12 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30577</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30582</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2776,7 +2751,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MANTA-30576</t>
+          <t>MANTA-30581</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2786,12 +2761,12 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30576</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30581</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>30987</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2818,7 +2793,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MANTA-30575</t>
+          <t>MANTA-30580</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2828,12 +2803,12 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30575</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30580</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>30981</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2860,7 +2835,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MANTA-30574</t>
+          <t>MANTA-30579</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2870,12 +2845,12 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30574</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30579</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>30980</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2890,7 +2865,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2902,7 +2877,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MANTA-30573</t>
+          <t>MANTA-30578</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2912,12 +2887,12 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30573</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30578</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2932,7 +2907,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2944,7 +2919,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MANTA-30571</t>
+          <t>MANTA-30577</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2954,12 +2929,12 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30571</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30577</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>30983</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2986,7 +2961,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MANTA-30570</t>
+          <t>MANTA-30576</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2996,12 +2971,12 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30570</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30576</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3028,7 +3003,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MANTA-30569</t>
+          <t>MANTA-30575</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3038,12 +3013,12 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30569</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30575</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3070,7 +3045,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MANTA-30568</t>
+          <t>MANTA-30574</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3080,12 +3055,12 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30568</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30574</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>30974</t>
+          <t>30980</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3095,24 +3070,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HONDA - WR-V - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MANTA-30567</t>
+          <t>MANTA-30573</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3122,12 +3097,12 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30567</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30573</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>30973</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3137,24 +3112,24 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>HONDA - NEW HR-V SUV - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MANTA-30530</t>
+          <t>MANTA-30571</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3164,12 +3139,12 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30530</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30571</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>30939</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3179,12 +3154,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3196,7 +3171,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MANTA-30512</t>
+          <t>MANTA-30570</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3206,12 +3181,12 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30570</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3238,7 +3213,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MANTA-30511</t>
+          <t>MANTA-30569</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3248,12 +3223,12 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30569</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>30920</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3280,7 +3255,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MANTA-30509</t>
+          <t>MANTA-30543</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3290,17 +3265,17 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30543</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>30918</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Liberado Engenharia</t>
+          <t>A Produzir</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3310,19 +3285,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>BMW - SERIE 3 SEDAN - 2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MANTA-30505</t>
+          <t>MANTA-30530</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3332,12 +3302,12 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30530</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3364,7 +3334,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MANTA-30479</t>
+          <t>MANTA-30520</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3374,12 +3344,12 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30479</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30520</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30892</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3394,19 +3364,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LEXUS - NX 350 H SUV - 2026</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>VOLVO - EX30 PLUS SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MANTA-30463</t>
+          <t>MANTA-30512</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3416,12 +3381,12 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3448,7 +3413,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MANTA-30452</t>
+          <t>MANTA-30511</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3458,12 +3423,12 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3473,12 +3438,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA CROSS - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3490,7 +3455,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MANTA-30451</t>
+          <t>MANTA-30509</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3500,12 +3465,12 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30451</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3515,24 +3480,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>KIA - CARNIVAL VAN - 2025</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MANTA-30428</t>
+          <t>MANTA-30505</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3542,12 +3507,12 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3562,7 +3527,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3574,7 +3539,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MANTA-30421</t>
+          <t>MANTA-30496</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3584,12 +3549,12 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3599,24 +3564,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>BMW - X3 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MANTA-30420</t>
+          <t>MANTA-30494</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3626,12 +3586,12 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3641,24 +3601,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>TOYOTA - RAV4 HEV SUV - 2025</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MANTA-30367</t>
+          <t>MANTA-30463</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3668,12 +3623,12 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3700,7 +3655,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MANTA-30257</t>
+          <t>MANTA-30458</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3710,12 +3665,12 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30458</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3730,19 +3685,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>GWM - HAVAL H6 PHEV 35 - 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MANTA-30242</t>
+          <t>MANTA-30452</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3752,12 +3702,12 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3777,14 +3727,14 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MANTA-30224</t>
+          <t>MANTA-30447</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3794,12 +3744,12 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30447</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30860</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3814,19 +3764,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>TOYOTA - SW4 SUV - 2026</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>BMW - X2 SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MANTA-30196</t>
+          <t>MANTA-30435</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3836,12 +3781,12 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30435</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>30848</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3851,24 +3796,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>JEEP - COMMANDER SUV - 2022</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MANTA-30191</t>
+          <t>MANTA-30428</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3878,12 +3818,12 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30191</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30428</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3893,24 +3833,24 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>BMW - X3 SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MANTA-30026</t>
+          <t>MANTA-30421</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3920,12 +3860,12 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-30026</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30421</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30834</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3935,24 +3875,24 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>⚪️RECEBIDO ENCAMINHADO</t>
+          <t>🟢RECEBIDO LIBERADO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JEEP - COMMANDER SUV - 2026</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MANTA-29923</t>
+          <t>MANTA-30420</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3962,12 +3902,12 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30420</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3987,14 +3927,14 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MANTA-29866</t>
+          <t>MANTA-30419</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4004,12 +3944,12 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4024,19 +3964,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MANTA-29816</t>
+          <t>MANTA-30403</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4046,12 +3981,12 @@
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4061,24 +3996,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
+          <t>FIAT - PULSE - 2024</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MANTA-29792</t>
+          <t>MANTA-30367</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4088,17 +4018,17 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>A Produzir</t>
+          <t>Liberado Engenharia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4108,19 +4038,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MANTA-29372</t>
+          <t>MANTA-30346</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4130,12 +4060,12 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>30766</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4145,24 +4075,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>🟢RECEBIDO LIBERADO</t>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>TOYOTA - COROLLA SEDAN - 2026</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>13/03/2026</t>
+          <t>JEEP - COMMANDER SUV - 2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MANTA-27100</t>
+          <t>MANTA-30265</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4172,12 +4097,12 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>https://carboncars.atlassian.net/browse/MANTA-27100</t>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4192,12 +4117,538 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>LEXUS - RX 500H SUV - 2025</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
+          <t>FORD - NOVA RANGER PICK-UP - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MANTA-30257</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30257</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>30687</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>TOYOTA - SW4 SUV - 2026</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MANTA-30242</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>30674</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>TOYOTA - COROLLA CROSS - 2026</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>10/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MANTA-30224</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30224</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>30657</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>TOYOTA - SW4 SUV - 2026</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MANTA-30196</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>30632</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MANTA-30191</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30191</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>30628</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>BMW - X3 SUV - 2026</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MANTA-30099</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>30556</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MANTA-30072</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30072</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>30529</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MANTA-30053</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>30510</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>⚪️RECEBIDO ENCAMINHADO</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>GWM - WEY 07 SUV - 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MANTA-29923</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MANTA-29866</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29866</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>30344</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MANTA-29816</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>30303</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MANTA-29792</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>30282</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MANTA-29372</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Manta</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>29901</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Liberado Engenharia</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>🟢RECEBIDO LIBERADO</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>TOYOTA - COROLLA SEDAN - 2026</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
         </is>
       </c>
     </row>
@@ -4292,6 +4743,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/jira_cards.xlsx
+++ b/src/jira_cards.xlsx
@@ -8,19 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guarino.silva\Documents\Maestro\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9090061-91D2-478C-9BB6-37DEB346FC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C489CA88-B206-4E34-B749-28317C05F0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$104</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="353">
   <si>
     <t>ID</t>
   </si>
@@ -46,141 +62,177 @@
     <t>DT. PREVISÃO ENTREGA</t>
   </si>
   <si>
+    <t>TENSYLON-825</t>
+  </si>
+  <si>
+    <t>Tensylon</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-825</t>
+  </si>
+  <si>
+    <t>31131</t>
+  </si>
+  <si>
+    <t>A Produzir</t>
+  </si>
+  <si>
+    <t>⚪️RECEBIDO ENCAMINHADO</t>
+  </si>
+  <si>
+    <t>HONDA - NEW HR-V SUV - 2026</t>
+  </si>
+  <si>
     <t>TENSYLON-818</t>
   </si>
   <si>
-    <t>Tensylon</t>
-  </si>
-  <si>
     <t>https://carboncars.atlassian.net/browse/TENSYLON-818</t>
   </si>
   <si>
     <t>31070</t>
   </si>
   <si>
+    <t>Aguardando montagem</t>
+  </si>
+  <si>
+    <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
+  </si>
+  <si>
+    <t>TENSYLON-816</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-816</t>
+  </si>
+  <si>
+    <t>30963</t>
+  </si>
+  <si>
+    <t>Aguardando Acabamento</t>
+  </si>
+  <si>
+    <t>🟢RECEBIDO LIBERADO</t>
+  </si>
+  <si>
+    <t>VOLVO - EX30 ULTRA SUV - 2026</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>TENSYLON-815</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-815</t>
+  </si>
+  <si>
+    <t>30956</t>
+  </si>
+  <si>
+    <t>LAND ROVER - NEW DISCOVERY SUV - 2026</t>
+  </si>
+  <si>
+    <t>TENSYLON-813</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-813</t>
+  </si>
+  <si>
+    <t>30949</t>
+  </si>
+  <si>
+    <t>BMW - SERIE 3 SEDAN - 2026</t>
+  </si>
+  <si>
+    <t>TENSYLON-812</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-812</t>
+  </si>
+  <si>
+    <t>30948</t>
+  </si>
+  <si>
+    <t>BMW - X3 SUV - 2026</t>
+  </si>
+  <si>
+    <t>TENSYLON-805</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-805</t>
+  </si>
+  <si>
+    <t>30905</t>
+  </si>
+  <si>
+    <t>Aguardando Corte</t>
+  </si>
+  <si>
+    <t>TENSYLON-801</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-801</t>
+  </si>
+  <si>
+    <t>30864</t>
+  </si>
+  <si>
+    <t>KIA - CARNIVAL VAN - 2025</t>
+  </si>
+  <si>
+    <t>TENSYLON-800</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-800</t>
+  </si>
+  <si>
+    <t>30861</t>
+  </si>
+  <si>
+    <t>LEXUS - NX 350 H SUV - 2026</t>
+  </si>
+  <si>
+    <t>TENSYLON-799</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-799</t>
+  </si>
+  <si>
+    <t>30840</t>
+  </si>
+  <si>
+    <t>PORSCHE - CAYENNE COUPE - 2026</t>
+  </si>
+  <si>
+    <t>TENSYLON-787</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-787</t>
+  </si>
+  <si>
+    <t>30772</t>
+  </si>
+  <si>
+    <t>TENSYLON-761</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-761</t>
+  </si>
+  <si>
+    <t>30628</t>
+  </si>
+  <si>
+    <t>TENSYLON-745</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/TENSYLON-745</t>
+  </si>
+  <si>
+    <t>30529</t>
+  </si>
+  <si>
     <t>Liberado Engenharia</t>
   </si>
   <si>
-    <t>⚪️RECEBIDO ENCAMINHADO</t>
-  </si>
-  <si>
-    <t>MINI - COOPER 02 PORTAS HATCH - 2025</t>
-  </si>
-  <si>
-    <t>TENSYLON-816</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-816</t>
-  </si>
-  <si>
-    <t>30963</t>
-  </si>
-  <si>
-    <t>Aguardando montagem</t>
-  </si>
-  <si>
-    <t>🟢RECEBIDO LIBERADO</t>
-  </si>
-  <si>
-    <t>VOLVO - EX30 ULTRA SUV - 2026</t>
-  </si>
-  <si>
-    <t>TENSYLON-815</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-815</t>
-  </si>
-  <si>
-    <t>30956</t>
-  </si>
-  <si>
-    <t>A Produzir</t>
-  </si>
-  <si>
-    <t>LAND ROVER - NEW DISCOVERY SUV - 2026</t>
-  </si>
-  <si>
-    <t>TENSYLON-813</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-813</t>
-  </si>
-  <si>
-    <t>30949</t>
-  </si>
-  <si>
-    <t>BMW - SERIE 3 SEDAN - 2026</t>
-  </si>
-  <si>
-    <t>TENSYLON-812</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-812</t>
-  </si>
-  <si>
-    <t>30948</t>
-  </si>
-  <si>
-    <t>BMW - X3 SUV - 2026</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
-    <t>TENSYLON-805</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-805</t>
-  </si>
-  <si>
-    <t>30905</t>
-  </si>
-  <si>
-    <t>TENSYLON-801</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-801</t>
-  </si>
-  <si>
-    <t>30864</t>
-  </si>
-  <si>
-    <t>KIA - CARNIVAL VAN - 2025</t>
-  </si>
-  <si>
-    <t>TENSYLON-799</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-799</t>
-  </si>
-  <si>
-    <t>30840</t>
-  </si>
-  <si>
-    <t>Aguardando Autoclave</t>
-  </si>
-  <si>
-    <t>PORSCHE - CAYENNE COUPE - 2026</t>
-  </si>
-  <si>
-    <t>TENSYLON-761</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-761</t>
-  </si>
-  <si>
-    <t>30628</t>
-  </si>
-  <si>
-    <t>TENSYLON-745</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/TENSYLON-745</t>
-  </si>
-  <si>
-    <t>30529</t>
-  </si>
-  <si>
     <t>GWM - HAVAL H6 PHEV 19 - 2026</t>
   </si>
   <si>
@@ -220,21 +272,30 @@
     <t>LAND ROVER - DISCOVERY SPORT SUV - 2023</t>
   </si>
   <si>
+    <t>MANTA-30765</t>
+  </si>
+  <si>
+    <t>Manta</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30765</t>
+  </si>
+  <si>
+    <t>31158</t>
+  </si>
+  <si>
+    <t>TOYOTA - COROLLA SEDAN - 2026</t>
+  </si>
+  <si>
     <t>MANTA-30763</t>
   </si>
   <si>
-    <t>Manta</t>
-  </si>
-  <si>
     <t>https://carboncars.atlassian.net/browse/MANTA-30763</t>
   </si>
   <si>
     <t>31136 - ALT</t>
   </si>
   <si>
-    <t>TOYOTA - COROLLA SEDAN - 2026</t>
-  </si>
-  <si>
     <t>13/03/2026</t>
   </si>
   <si>
@@ -250,6 +311,18 @@
     <t>BMW - X1 SUV - 2026</t>
   </si>
   <si>
+    <t>MANTA-30753</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30753</t>
+  </si>
+  <si>
+    <t>31121 - ALT</t>
+  </si>
+  <si>
+    <t>TOYOTA - SW4 SUV - 2020</t>
+  </si>
+  <si>
     <t>MANTA-30740</t>
   </si>
   <si>
@@ -325,6 +398,12 @@
     <t>TOYOTA - COROLLA CROSS - 2026</t>
   </si>
   <si>
+    <t>MANTA-30731</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30731</t>
+  </si>
+  <si>
     <t>MANTA-30730</t>
   </si>
   <si>
@@ -364,22 +443,64 @@
     <t>31120</t>
   </si>
   <si>
-    <t>MANTA-30670</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30670</t>
-  </si>
-  <si>
-    <t>31073</t>
-  </si>
-  <si>
-    <t>GWM - HAVAL H6 HEV 2 - 2026</t>
-  </si>
-  <si>
-    <t>MANTA-30667</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30667</t>
+    <t>MANTA-30694</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30694</t>
+  </si>
+  <si>
+    <t>31097</t>
+  </si>
+  <si>
+    <t>JEEP - COMPASS SUV - 2026</t>
+  </si>
+  <si>
+    <t>MANTA-30691</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30691</t>
+  </si>
+  <si>
+    <t>31094</t>
+  </si>
+  <si>
+    <t>AUDI - A5 SEDAN - 2025</t>
+  </si>
+  <si>
+    <t>MANTA-30689</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30689</t>
+  </si>
+  <si>
+    <t>31092</t>
+  </si>
+  <si>
+    <t>TOYOTA - HILUX CABINE DUPLA PICK-UP - 2026</t>
+  </si>
+  <si>
+    <t>MANTA-30683</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30683</t>
+  </si>
+  <si>
+    <t>31086</t>
+  </si>
+  <si>
+    <t>GWM - HAVAL H6 GT - 2026</t>
+  </si>
+  <si>
+    <t>MANTA-30675</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30675</t>
+  </si>
+  <si>
+    <t>31078</t>
+  </si>
+  <si>
+    <t>HONDA - NEW CR-V SUV - 2024</t>
   </si>
   <si>
     <t>MANTA-30658</t>
@@ -430,18 +551,6 @@
     <t>31054</t>
   </si>
   <si>
-    <t>MANTA-30636</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30636</t>
-  </si>
-  <si>
-    <t>31041</t>
-  </si>
-  <si>
-    <t>FORD - MUSTANG GT - 2025</t>
-  </si>
-  <si>
     <t>MANTA-30624</t>
   </si>
   <si>
@@ -745,6 +854,15 @@
     <t>https://carboncars.atlassian.net/browse/MANTA-30543</t>
   </si>
   <si>
+    <t>MANTA-30534</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30534</t>
+  </si>
+  <si>
+    <t>30942</t>
+  </si>
+  <si>
     <t>MANTA-30530</t>
   </si>
   <si>
@@ -754,180 +872,147 @@
     <t>30939</t>
   </si>
   <si>
-    <t>MANTA-30520</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30520</t>
-  </si>
-  <si>
-    <t>30929</t>
+    <t>MANTA-30529</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30529</t>
+  </si>
+  <si>
+    <t>30938</t>
+  </si>
+  <si>
+    <t>LEXUS - RX 450H SUV - 2026</t>
+  </si>
+  <si>
+    <t>MANTA-30512</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
+  </si>
+  <si>
+    <t>30921</t>
+  </si>
+  <si>
+    <t>MANTA-30511</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
+  </si>
+  <si>
+    <t>30920</t>
+  </si>
+  <si>
+    <t>MANTA-30509</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
+  </si>
+  <si>
+    <t>30918</t>
+  </si>
+  <si>
+    <t>MANTA-30505</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
+  </si>
+  <si>
+    <t>30914</t>
+  </si>
+  <si>
+    <t>MANTA-30496</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
+  </si>
+  <si>
+    <t>MANTA-30494</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
+  </si>
+  <si>
+    <t>30903</t>
+  </si>
+  <si>
+    <t>TOYOTA - RAV4 HEV SUV - 2025</t>
+  </si>
+  <si>
+    <t>MANTA-30461</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30461</t>
+  </si>
+  <si>
+    <t>30874</t>
+  </si>
+  <si>
+    <t>MANTA-30452</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
+  </si>
+  <si>
+    <t>30865</t>
+  </si>
+  <si>
+    <t>MANTA-30448</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30448</t>
+  </si>
+  <si>
+    <t>MANTA-30446</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30446</t>
+  </si>
+  <si>
+    <t>30859</t>
+  </si>
+  <si>
+    <t>MANTA-30419</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
+  </si>
+  <si>
+    <t>30832</t>
+  </si>
+  <si>
+    <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
+  </si>
+  <si>
+    <t>MANTA-30403</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
+  </si>
+  <si>
+    <t>30816</t>
+  </si>
+  <si>
+    <t>FIAT - PULSE - 2024</t>
+  </si>
+  <si>
+    <t>MANTA-30352</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30352</t>
+  </si>
+  <si>
+    <t>MANTA-30330</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30330</t>
+  </si>
+  <si>
+    <t>30756</t>
   </si>
   <si>
     <t>VOLVO - EX30 PLUS SUV - 2026</t>
   </si>
   <si>
-    <t>MANTA-30512</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30512</t>
-  </si>
-  <si>
-    <t>30921</t>
-  </si>
-  <si>
-    <t>MANTA-30511</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30511</t>
-  </si>
-  <si>
-    <t>30920</t>
-  </si>
-  <si>
-    <t>MANTA-30509</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30509</t>
-  </si>
-  <si>
-    <t>30918</t>
-  </si>
-  <si>
-    <t>MANTA-30505</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30505</t>
-  </si>
-  <si>
-    <t>30914</t>
-  </si>
-  <si>
-    <t>MANTA-30496</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30496</t>
-  </si>
-  <si>
-    <t>MANTA-30494</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30494</t>
-  </si>
-  <si>
-    <t>30903</t>
-  </si>
-  <si>
-    <t>TOYOTA - RAV4 HEV SUV - 2025</t>
-  </si>
-  <si>
-    <t>MANTA-30463</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30463</t>
-  </si>
-  <si>
-    <t>30876</t>
-  </si>
-  <si>
-    <t>MANTA-30458</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30458</t>
-  </si>
-  <si>
-    <t>30871</t>
-  </si>
-  <si>
-    <t>GWM - HAVAL H6 PHEV 35 - 2026</t>
-  </si>
-  <si>
-    <t>MANTA-30452</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30452</t>
-  </si>
-  <si>
-    <t>30865</t>
-  </si>
-  <si>
-    <t>MANTA-30447</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30447</t>
-  </si>
-  <si>
-    <t>30860</t>
-  </si>
-  <si>
-    <t>BMW - X2 SUV - 2026</t>
-  </si>
-  <si>
-    <t>MANTA-30435</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30435</t>
-  </si>
-  <si>
-    <t>30848</t>
-  </si>
-  <si>
-    <t>JEEP - COMMANDER SUV - 2022</t>
-  </si>
-  <si>
-    <t>MANTA-30419</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30419</t>
-  </si>
-  <si>
-    <t>30832</t>
-  </si>
-  <si>
-    <t>LAND ROVER - NEW RANGE ROVER SPORT SUV - 2026</t>
-  </si>
-  <si>
-    <t>MANTA-30403</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30403</t>
-  </si>
-  <si>
-    <t>30816</t>
-  </si>
-  <si>
-    <t>FIAT - PULSE - 2024</t>
-  </si>
-  <si>
-    <t>MANTA-30367</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30367</t>
-  </si>
-  <si>
-    <t>30786</t>
-  </si>
-  <si>
-    <t>MANTA-30346</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30346</t>
-  </si>
-  <si>
-    <t>30766</t>
-  </si>
-  <si>
-    <t>MANTA-30265</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30265</t>
-  </si>
-  <si>
-    <t>30693</t>
-  </si>
-  <si>
-    <t>FORD - NOVA RANGER PICK-UP - 2026</t>
-  </si>
-  <si>
     <t>MANTA-30257</t>
   </si>
   <si>
@@ -937,15 +1022,6 @@
     <t>30687</t>
   </si>
   <si>
-    <t>MANTA-30242</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30242</t>
-  </si>
-  <si>
-    <t>30674</t>
-  </si>
-  <si>
     <t>MANTA-30224</t>
   </si>
   <si>
@@ -955,22 +1031,13 @@
     <t>30657</t>
   </si>
   <si>
-    <t>MANTA-30196</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30196</t>
-  </si>
-  <si>
-    <t>30632</t>
-  </si>
-  <si>
-    <t>MANTA-30099</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-30099</t>
-  </si>
-  <si>
-    <t>30556</t>
+    <t>MANTA-30172</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-30172</t>
+  </si>
+  <si>
+    <t>30612</t>
   </si>
   <si>
     <t>MANTA-30072</t>
@@ -985,13 +1052,16 @@
     <t>https://carboncars.atlassian.net/browse/MANTA-30053</t>
   </si>
   <si>
-    <t>MANTA-29923</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-29923</t>
-  </si>
-  <si>
-    <t>30392</t>
+    <t>MANTA-29977</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-29977</t>
+  </si>
+  <si>
+    <t>30442</t>
+  </si>
+  <si>
+    <t>GWM - TANK 300 SUV - 2026</t>
   </si>
   <si>
     <t>MANTA-29866</t>
@@ -1006,41 +1076,32 @@
     <t>LAND ROVER - DISCOVERY METROPOLITAN - 2024</t>
   </si>
   <si>
-    <t>MANTA-29816</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-29816</t>
-  </si>
-  <si>
-    <t>30303</t>
-  </si>
-  <si>
-    <t>MERCEDES-BENZ - EQS 450+ SUV - 2024</t>
-  </si>
-  <si>
-    <t>MANTA-29792</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-29792</t>
-  </si>
-  <si>
-    <t>30282</t>
-  </si>
-  <si>
-    <t>MANTA-29372</t>
-  </si>
-  <si>
-    <t>https://carboncars.atlassian.net/browse/MANTA-29372</t>
-  </si>
-  <si>
-    <t>29901</t>
+    <t>MANTA-29549</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-29549</t>
+  </si>
+  <si>
+    <t>30059</t>
+  </si>
+  <si>
+    <t>MANTA-28595</t>
+  </si>
+  <si>
+    <t>https://carboncars.atlassian.net/browse/MANTA-28595</t>
+  </si>
+  <si>
+    <t>29222</t>
+  </si>
+  <si>
+    <t>TOYOTA - COROLLA SEDAN - 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1055,13 +1116,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1077,9 +1158,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1383,17 +1467,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -1424,2605 +1508,2682 @@
     </row>
     <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" t="s">
-        <v>44</v>
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>306</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>312</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>328</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>329</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>330</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>331</v>
-      </c>
-      <c r="H12" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>333</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>334</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>331</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
+        <v>62</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>78</v>
+      <c r="D15" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" t="s">
-        <v>71</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>270</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>89</v>
+        <v>271</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>96</v>
+        <v>88</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
+        <v>301</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>302</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>346</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>103</v>
+        <v>347</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>348</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
-      </c>
-      <c r="H22" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>110</v>
+        <v>295</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
-      </c>
-      <c r="H23" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>315</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>112</v>
+        <v>316</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>317</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" t="s">
-        <v>71</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D25" t="s">
-        <v>122</v>
+        <v>165</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
-      </c>
-      <c r="H25" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
+        <v>148</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>334</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27" t="s">
-        <v>128</v>
+        <v>335</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" t="s">
-        <v>135</v>
+        <v>339</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>340</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" t="s">
-        <v>71</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>336</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D29" t="s">
-        <v>142</v>
+        <v>337</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
-      </c>
-      <c r="H29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
-      </c>
-      <c r="H30" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
-      </c>
-      <c r="H31" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" t="s">
-        <v>151</v>
+        <v>273</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>274</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
-      </c>
-      <c r="H32" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
+        <v>320</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>100</v>
-      </c>
-      <c r="H33" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D34" t="s">
-        <v>157</v>
+        <v>136</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>158</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>344</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="H35" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>162</v>
+        <v>312</v>
       </c>
       <c r="D36" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" t="s">
-        <v>100</v>
-      </c>
-      <c r="H36" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" t="s">
-        <v>166</v>
+        <v>307</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
-      </c>
-      <c r="H37" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D38" t="s">
-        <v>169</v>
+        <v>279</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>280</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
-      </c>
-      <c r="H38" t="s">
-        <v>71</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H39" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H40" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H41" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H42" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="E43" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H43" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H44" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H45" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D46" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
-      </c>
-      <c r="G46" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H46" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D47" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
-      </c>
-      <c r="G47" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H47" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D48" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H48" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E49" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H49" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D50" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="E50" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
-      </c>
-      <c r="G50" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H50" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D51" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E51" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F51" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H51" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D52" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E52" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H52" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D53" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E53" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F53" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H53" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D54" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G54" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H54" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D55" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H55" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="D56" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
-      </c>
-      <c r="G56" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H56" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H57" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>228</v>
+        <v>276</v>
       </c>
       <c r="D58" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H58" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>231</v>
+        <v>289</v>
       </c>
       <c r="D59" t="s">
-        <v>232</v>
+        <v>290</v>
       </c>
       <c r="E59" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H59" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="D60" t="s">
-        <v>235</v>
+        <v>293</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
-      </c>
-      <c r="G60" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H60" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="D61" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
       <c r="E61" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H61" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>241</v>
+        <v>349</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>242</v>
+        <v>350</v>
       </c>
       <c r="D62" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="E62" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" t="s">
-        <v>100</v>
-      </c>
-      <c r="H62" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="D63" t="s">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" t="s">
-        <v>70</v>
-      </c>
-      <c r="H63" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>252</v>
+        <v>84</v>
       </c>
       <c r="D64" t="s">
-        <v>253</v>
+        <v>85</v>
       </c>
       <c r="E64" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H64" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>254</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>255</v>
+        <v>96</v>
       </c>
       <c r="D65" t="s">
-        <v>256</v>
+        <v>97</v>
       </c>
       <c r="E65" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H65" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>257</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>258</v>
+        <v>99</v>
       </c>
       <c r="D66" t="s">
-        <v>259</v>
+        <v>100</v>
       </c>
       <c r="E66" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H66" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>266</v>
+        <v>101</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>267</v>
+        <v>102</v>
       </c>
       <c r="D67" t="s">
-        <v>268</v>
+        <v>103</v>
       </c>
       <c r="E67" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H67" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>273</v>
+        <v>104</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>274</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>275</v>
+        <v>106</v>
       </c>
       <c r="E68" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H68" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>292</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>293</v>
+        <v>108</v>
       </c>
       <c r="D69" t="s">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="E69" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
-      </c>
-      <c r="G69" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H69" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>302</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>303</v>
+        <v>111</v>
       </c>
       <c r="D70" t="s">
-        <v>304</v>
+        <v>112</v>
       </c>
       <c r="E70" t="s">
         <v>12</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
-      </c>
-      <c r="G70" t="s">
-        <v>107</v>
+        <v>24</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H70" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>308</v>
+        <v>113</v>
       </c>
       <c r="B71" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>309</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="E71" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
-      </c>
-      <c r="G71" t="s">
-        <v>107</v>
+        <v>24</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H71" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>321</v>
+        <v>168</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>322</v>
+        <v>169</v>
       </c>
       <c r="D72" t="s">
-        <v>323</v>
+        <v>170</v>
       </c>
       <c r="E72" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
-      </c>
-      <c r="G72" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H72" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>324</v>
+        <v>171</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>325</v>
+        <v>172</v>
       </c>
       <c r="D73" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="E73" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F73" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" t="s">
-        <v>327</v>
+        <v>24</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H73" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>335</v>
+        <v>174</v>
       </c>
       <c r="B74" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>336</v>
+        <v>175</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>176</v>
       </c>
       <c r="E74" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F74" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" t="s">
-        <v>70</v>
+        <v>24</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H74" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="D75" t="s">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="E75" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H75" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="D77" t="s">
-        <v>28</v>
+        <v>209</v>
       </c>
       <c r="E77" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>36</v>
+        <v>211</v>
       </c>
       <c r="D78" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="E78" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" t="s">
-        <v>33</v>
+        <v>24</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>213</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>51</v>
+        <v>214</v>
       </c>
       <c r="D79" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="E79" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" t="s">
-        <v>53</v>
+        <v>24</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>216</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>55</v>
+        <v>217</v>
       </c>
       <c r="D80" t="s">
-        <v>56</v>
+        <v>218</v>
       </c>
       <c r="E80" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>72</v>
+        <v>225</v>
       </c>
       <c r="B81" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="D81" t="s">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="E81" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H81" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="E82" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H82" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>114</v>
+        <v>231</v>
       </c>
       <c r="B83" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>115</v>
+        <v>232</v>
       </c>
       <c r="D83" t="s">
-        <v>116</v>
+        <v>233</v>
       </c>
       <c r="E83" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="B84" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="D84" t="s">
-        <v>11</v>
+        <v>236</v>
       </c>
       <c r="E84" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H84" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>129</v>
+        <v>237</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="D85" t="s">
-        <v>131</v>
+        <v>239</v>
       </c>
       <c r="E85" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H85" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="B86" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="D86" t="s">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="E86" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>245</v>
       </c>
       <c r="E87" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B88" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D88" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E88" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B89" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D89" t="s">
+        <v>251</v>
+      </c>
+      <c r="E89" t="s">
+        <v>64</v>
+      </c>
+      <c r="F89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H89" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>252</v>
+      </c>
+      <c r="B90" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D90" t="s">
+        <v>254</v>
+      </c>
+      <c r="E90" t="s">
+        <v>64</v>
+      </c>
+      <c r="F90" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H90" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>261</v>
       </c>
-      <c r="D89" t="s">
-        <v>37</v>
-      </c>
-      <c r="E89" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="B91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B90" t="s">
-        <v>67</v>
-      </c>
-      <c r="C90" s="1" t="s">
+      <c r="D91" t="s">
         <v>263</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E91" t="s">
+        <v>64</v>
+      </c>
+      <c r="F91" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H91" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>264</v>
       </c>
-      <c r="E90" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="B92" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="D92" t="s">
+        <v>266</v>
+      </c>
+      <c r="E92" t="s">
+        <v>64</v>
+      </c>
+      <c r="F92" t="s">
+        <v>24</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H92" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>267</v>
+      </c>
+      <c r="B93" t="s">
+        <v>79</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D93" t="s">
         <v>269</v>
       </c>
-      <c r="B91" t="s">
-        <v>67</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D91" t="s">
-        <v>271</v>
-      </c>
-      <c r="E91" t="s">
-        <v>12</v>
-      </c>
-      <c r="F91" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>276</v>
-      </c>
-      <c r="B92" t="s">
-        <v>67</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D92" t="s">
-        <v>278</v>
-      </c>
-      <c r="E92" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>280</v>
-      </c>
-      <c r="B93" t="s">
-        <v>67</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
+        <v>64</v>
+      </c>
+      <c r="F93" t="s">
+        <v>24</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H93" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>282</v>
       </c>
-      <c r="E93" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" t="s">
+      <c r="B94" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="D94" t="s">
         <v>284</v>
       </c>
-      <c r="B94" t="s">
-        <v>67</v>
-      </c>
-      <c r="C94" s="1" t="s">
+      <c r="E94" t="s">
+        <v>64</v>
+      </c>
+      <c r="F94" t="s">
+        <v>24</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H94" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>285</v>
       </c>
-      <c r="D94" t="s">
+      <c r="B95" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E94" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" t="s">
+      <c r="D95" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>288</v>
-      </c>
-      <c r="B95" t="s">
-        <v>67</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D95" t="s">
-        <v>290</v>
-      </c>
       <c r="E95" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H95" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>295</v>
+        <v>143</v>
       </c>
       <c r="B96" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>296</v>
+        <v>144</v>
       </c>
       <c r="D96" t="s">
-        <v>297</v>
+        <v>145</v>
       </c>
       <c r="E96" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F96" t="s">
         <v>13</v>
       </c>
-      <c r="G96" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G96" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B97" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D97" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E97" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F97" t="s">
         <v>13</v>
       </c>
-      <c r="G97" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G97" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B98" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="D98" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="E98" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F98" t="s">
         <v>13</v>
       </c>
-      <c r="G98" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G98" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>317</v>
+        <v>91</v>
       </c>
       <c r="B99" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>318</v>
+        <v>92</v>
       </c>
       <c r="D99" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="E99" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F99" t="s">
         <v>13</v>
       </c>
-      <c r="G99" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="G99" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>319</v>
+        <v>125</v>
       </c>
       <c r="B100" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="D100" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="E100" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F100" t="s">
         <v>13</v>
       </c>
-      <c r="G100" t="s">
-        <v>57</v>
+      <c r="G100" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>325</v>
+      </c>
+      <c r="B101" t="s">
+        <v>79</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D101" t="s">
+        <v>327</v>
+      </c>
+      <c r="E101" t="s">
+        <v>64</v>
+      </c>
+      <c r="F101" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H101" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>328</v>
+      </c>
+      <c r="B102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D102" t="s">
+        <v>330</v>
+      </c>
+      <c r="E102" t="s">
+        <v>64</v>
+      </c>
+      <c r="F102" t="s">
+        <v>24</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H102" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>331</v>
+      </c>
+      <c r="B103" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D103" t="s">
+        <v>333</v>
+      </c>
+      <c r="E103" t="s">
+        <v>64</v>
+      </c>
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>321</v>
+      </c>
+      <c r="B104" t="s">
+        <v>79</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E104" t="s">
+        <v>64</v>
+      </c>
+      <c r="F104" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
-    <sortCondition ref="H2:H100"/>
-  </sortState>
+  <autoFilter ref="A1:H104" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:H104">
+      <sortCondition ref="G1:G104"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C75" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C76" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C77" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C78" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="C8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C3" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C79" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C80" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C10" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C4" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C81" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="C15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C17" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C11" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C20" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C21" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C22" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C82" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C23" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C24" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C83" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C84" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C25" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C26" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C27" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C85" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C28" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C86" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C29" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C30" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C31" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C32" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C33" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C34" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C35" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C36" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C37" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C38" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C39" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C40" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C41" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C42" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C43" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C44" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C45" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C46" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C47" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C48" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C49" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C50" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C51" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C52" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C53" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C54" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C55" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C56" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C57" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C58" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C59" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C60" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C61" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C87" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C62" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C88" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C63" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C64" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C65" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C66" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C89" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C90" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C67" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C91" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C68" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C92" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C93" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C94" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C95" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C69" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C96" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C97" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C70" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C5" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C71" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C6" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C98" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C99" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="C100" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="C72" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="C73" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="C12" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="C13" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="C74" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C63" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C64" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C99" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C65" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C66" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C67" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C68" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C69" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C70" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C71" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C39" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C40" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C100" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C41" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C42" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C34" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C18" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C96" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C26" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C30" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C43" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C44" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C45" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C25" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C72" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C73" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C74" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C75" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C46" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C49" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C50" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C76" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C51" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C52" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C53" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C77" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C78" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C79" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C80" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C54" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C55" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C81" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C82" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C83" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C84" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C85" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C86" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C87" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C88" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C89" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C90" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C56" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C57" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C91" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C92" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C93" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C19" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C32" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C58" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C38" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C94" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C95" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C59" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C60" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C23" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C98" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C21" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C61" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C37" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C97" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C36" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C24" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C33" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C104" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C101" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C102" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C103" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C27" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C29" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C28" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C35" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C22" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C62" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="D2:D17" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>